--- a/Scraping scripts/zorginstituut/zorginstituut_categorized_cancer_data.xlsx
+++ b/Scraping scripts/zorginstituut/zorginstituut_categorized_cancer_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="219">
   <si>
     <t>Advisory Topic</t>
   </si>
@@ -25,6 +25,12 @@
     <t>Source URL</t>
   </si>
   <si>
+    <t>Scrape Date</t>
+  </si>
+  <si>
+    <t>Content Hash</t>
+  </si>
+  <si>
     <t>Intro Summary</t>
   </si>
   <si>
@@ -257,6 +263,210 @@
   </si>
   <si>
     <t>https://www.zorginstituutnederland.nl/werkagenda/kanker/pakketadvies-sluisgeneesmiddel-trastuzumab-deruxtecan-enhertu-voor-de-behandeling-van-niet-kleincellige-longkanker-met-her2-mutatie</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:45:41</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:45:43</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:45:45</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:45:47</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:45:49</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:45:51</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:45:53</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:45:55</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:45:57</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:45:59</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:02</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:04</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:06</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:08</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:10</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:12</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:14</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:16</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:18</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:20</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:22</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:24</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:26</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:29</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:31</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:33</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:35</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:37</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:39</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:41</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:43</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:45</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:47</t>
+  </si>
+  <si>
+    <t>2026-05-31 14:46:49</t>
+  </si>
+  <si>
+    <t>6036d93ddc73cc055b97bd4abbd540487ff58757b7457066c7d54bfb675f23d1</t>
+  </si>
+  <si>
+    <t>868be5de8688b86bd7c499c3043296d8d1c72d3e089a7993d785d146164296c3</t>
+  </si>
+  <si>
+    <t>6ef7c56eb223441b02bdac8ff46bdb619422506be04da9923d17228cd795c57d</t>
+  </si>
+  <si>
+    <t>6c7c887d3805b71e914ec337ee88ba87ecb62e18dc82b5e946bc9da0e5485ab1</t>
+  </si>
+  <si>
+    <t>95991486db066a8f01d043ac03a2111c6248075c4e79950357c04ce9ba516bb3</t>
+  </si>
+  <si>
+    <t>b010dfede2ec91e6ab23ab9a4233e63109ad3fc702ebf674f868ab2bf8b38350</t>
+  </si>
+  <si>
+    <t>b6d1fb62ed9ff0916c2f0cf130e6efc3d4247eccbd9a18e66eac51c01f679133</t>
+  </si>
+  <si>
+    <t>490638abd33c252ca51c754f96a3e1783b94c1458a06ec4cd046ac89656560eb</t>
+  </si>
+  <si>
+    <t>3a09249ad61620a6891099b19c2cd5cad9000483a703d2e274cd79ad69526d95</t>
+  </si>
+  <si>
+    <t>2a2f9073403adac0bad9de742f2baca5f6c4b390d5cbab64438c067965562f86</t>
+  </si>
+  <si>
+    <t>7539a8626cfd34c3bfe773b720043b41ec97f90a8467ad09e72b89276eb0ad31</t>
+  </si>
+  <si>
+    <t>961674c524c279d8d98de6d56761eca85b5710e7fd2c340d2cc33c533b5632d2</t>
+  </si>
+  <si>
+    <t>b25f70cbcf3bac982c7f8bc42c59e45dac2284513e94deac34bed9705742e9af</t>
+  </si>
+  <si>
+    <t>db18dfb1daa4e71951e550282ee00022d43b2592e69c531e31e31483a61b5fb4</t>
+  </si>
+  <si>
+    <t>a52365e24b8d17e615bba1880faf9c7c80e4fe07a011fd72677b70ba8e0d569c</t>
+  </si>
+  <si>
+    <t>15e1b30c7c2db1c373b9bcc77a12a4d9f5cda1b776bb1a3db582e8b8e0fd61c5</t>
+  </si>
+  <si>
+    <t>ede4f224e7442ee35bc72bafa3652068c989b627c14301dd6dde2d1a386e2890</t>
+  </si>
+  <si>
+    <t>f09c2f648ccda407c061b076612d32d8c789af151e2d43bdea8e00bcbfa1af9f</t>
+  </si>
+  <si>
+    <t>ef51bda597f2855e6d2a660431796658c9693f322c38bd53e4c550cdb134eb7b</t>
+  </si>
+  <si>
+    <t>e961719f74c5037f5b89ed42232596c3ab1a0fcbf5460500d8d6683110d7718c</t>
+  </si>
+  <si>
+    <t>4e40c0b1871694f4ced008db77652c954843f516db7783d3bd38157f704f320f</t>
+  </si>
+  <si>
+    <t>8a8669ffcee7a5bba5234a1c2dfdd67ac612a947b4f17a18814b726cdc3ae5fe</t>
+  </si>
+  <si>
+    <t>6ef259b38a0bba6acd3971939e477cf0519ce4599b0f91831354dccd7b68d7ae</t>
+  </si>
+  <si>
+    <t>c46aac7a20855435110ed230e78cbe9accab498b2448a78ec457df4b881dc12d</t>
+  </si>
+  <si>
+    <t>4708f68a750dac3ca064ae984c544b648d722edaea883e8624b119ac2ae35d76</t>
+  </si>
+  <si>
+    <t>c229cd620d9320ed2988201c1b628a306ea22b036b42e5e92e3ef72f073266a7</t>
+  </si>
+  <si>
+    <t>f0c80695b6876e885c5e3fe859722da1f55b27ee01600ab3669bd3a49ae05277</t>
+  </si>
+  <si>
+    <t>0c5d7a114b8f30803ba2620a45f388cfff49d5ebc728ec3874e52a3466ae562f</t>
+  </si>
+  <si>
+    <t>8ba3b6b6c752b8ef9185ac1feaf9836b8f402692d83418da23e0a4d62b667b14</t>
+  </si>
+  <si>
+    <t>6349599cca64b61032be31494d169ecd4440f960ee6d2d18df300c7db88f3634</t>
+  </si>
+  <si>
+    <t>fbc215811a9fd9e32aebc1dad53af1e897e24841b93a74c8a207d85a015ada1c</t>
+  </si>
+  <si>
+    <t>83f2532a70c50d16c44422c28cabea86de3c4e75bd41b19e2cabd1d2b2d882aa</t>
+  </si>
+  <si>
+    <t>12e3f826c875398945cec6a85563358782a2bfc1f29abf118b323c17a775a3ac</t>
+  </si>
+  <si>
+    <t>c7ec5a7d44414bc08e5d6302a3633730b7bccb5f363199b21b97022880851293</t>
   </si>
   <si>
     <t>Zorginstituut Nederland evalueert de toepassing van het standpunt AFT na een totale borstverwijdering voor een bepaalde groep vrouwen. AFT staat voor autologe vettransplantatie met externe weefselexpansie. Hierbij evalueert het Zorginstituut de passende organisatie en inzet van AFT bij deze patiëntengroep, volgens de afspraken in het standpunt en het bijbehorende waarborgendocument.</t>
@@ -1599,10 +1809,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1618,583 +1828,793 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" t="s">
+        <v>158</v>
+      </c>
+      <c r="G9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F10" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" t="s">
+        <v>127</v>
+      </c>
+      <c r="F12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" t="s">
+        <v>163</v>
+      </c>
+      <c r="G14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15" t="s">
+        <v>164</v>
+      </c>
+      <c r="G15" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16" t="s">
+        <v>165</v>
+      </c>
+      <c r="G16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18" t="s">
+        <v>167</v>
+      </c>
+      <c r="G18" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" t="s">
+        <v>169</v>
+      </c>
+      <c r="G20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" t="s">
+        <v>170</v>
+      </c>
+      <c r="G21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" t="s">
+        <v>171</v>
+      </c>
+      <c r="G22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" t="s">
+        <v>172</v>
+      </c>
+      <c r="G23" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" t="s">
+        <v>173</v>
+      </c>
+      <c r="G24" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" t="s">
+        <v>107</v>
+      </c>
+      <c r="E26" t="s">
+        <v>141</v>
+      </c>
+      <c r="F26" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" t="s">
+        <v>142</v>
+      </c>
+      <c r="F27" t="s">
+        <v>176</v>
+      </c>
+      <c r="G27" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" t="s">
+        <v>144</v>
+      </c>
+      <c r="F29" t="s">
+        <v>178</v>
+      </c>
+      <c r="G29" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" t="s">
+        <v>145</v>
+      </c>
+      <c r="F30" t="s">
+        <v>179</v>
+      </c>
+      <c r="G30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" t="s">
+        <v>180</v>
+      </c>
+      <c r="G31" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" t="s">
+        <v>147</v>
+      </c>
+      <c r="F32" t="s">
+        <v>181</v>
+      </c>
+      <c r="G32" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" t="s">
+        <v>148</v>
+      </c>
+      <c r="F33" t="s">
+        <v>182</v>
+      </c>
+      <c r="G33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D34" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E34" t="s">
+        <v>149</v>
+      </c>
+      <c r="F34" t="s">
+        <v>183</v>
+      </c>
+      <c r="G34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D35" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" t="s">
-        <v>101</v>
-      </c>
-      <c r="E22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" t="s">
-        <v>114</v>
-      </c>
       <c r="E35" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="F35" t="s">
+        <v>184</v>
+      </c>
+      <c r="G35" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
